--- a/y11581/samples/shift_records.xlsx
+++ b/y11581/samples/shift_records.xlsx
@@ -504,22 +504,22 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>3021</v>
+        <v>3614</v>
       </c>
       <c r="F2">
-        <v>5916</v>
+        <v>5576</v>
       </c>
       <c r="G2">
-        <v>1548</v>
+        <v>583</v>
       </c>
       <c r="H2">
-        <v>831</v>
+        <v>1488</v>
       </c>
       <c r="I2">
-        <v>1840</v>
+        <v>1541</v>
       </c>
       <c r="J2">
-        <v>493</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -536,22 +536,22 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>4361</v>
+        <v>2108</v>
       </c>
       <c r="F3">
-        <v>6707</v>
+        <v>5435</v>
       </c>
       <c r="G3">
-        <v>1512</v>
+        <v>1847</v>
       </c>
       <c r="H3">
-        <v>1595</v>
+        <v>505</v>
       </c>
       <c r="I3">
-        <v>1208</v>
+        <v>1884</v>
       </c>
       <c r="J3">
-        <v>374</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -565,25 +565,25 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>2873</v>
+        <v>1931</v>
       </c>
       <c r="F4">
-        <v>6335</v>
+        <v>4185</v>
       </c>
       <c r="G4">
-        <v>1907</v>
+        <v>750</v>
       </c>
       <c r="H4">
-        <v>1962</v>
+        <v>1102</v>
       </c>
       <c r="I4">
-        <v>1841</v>
+        <v>1742</v>
       </c>
       <c r="J4">
-        <v>286</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -597,25 +597,25 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>2203</v>
+        <v>1595</v>
       </c>
       <c r="F5">
-        <v>4889</v>
+        <v>4546</v>
       </c>
       <c r="G5">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H5">
-        <v>1950</v>
+        <v>825</v>
       </c>
       <c r="I5">
-        <v>1040</v>
+        <v>1173</v>
       </c>
       <c r="J5">
-        <v>246</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -629,25 +629,25 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>4793</v>
+        <v>4182</v>
       </c>
       <c r="F6">
-        <v>9621</v>
+        <v>7202</v>
       </c>
       <c r="G6">
-        <v>1963</v>
+        <v>1328</v>
       </c>
       <c r="H6">
-        <v>1161</v>
+        <v>1999</v>
       </c>
       <c r="I6">
-        <v>2992</v>
+        <v>1930</v>
       </c>
       <c r="J6">
-        <v>127</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:10">
